--- a/artfynd/A 62620-2025 artfynd.xlsx
+++ b/artfynd/A 62620-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130930173</v>
+        <v>130926030</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473286</v>
+        <v>473268</v>
       </c>
       <c r="R2" t="n">
-        <v>6781163</v>
+        <v>6781239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på några tallar i omgivningen</t>
+          <t>3 bilder, 1 som miljöbild på torrakor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130930241</v>
+        <v>130926976</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473245</v>
+        <v>473279</v>
       </c>
       <c r="R3" t="n">
-        <v>6781194</v>
+        <v>6781233</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på flera tallar i omgivningen</t>
+          <t>1 bild på tall. Rikligt på flera tallar i omgivningen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130929811</v>
+        <v>130927174</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -928,16 +928,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473446</v>
+        <v>473354</v>
       </c>
       <c r="R4" t="n">
-        <v>6781033</v>
+        <v>6781177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +985,18 @@
           <t>13:26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på några stammar i omgivningen. 3 Miljöbilder för området</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,14 +1015,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130929896</v>
+        <v>130928099</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473383</v>
+        <v>473380</v>
       </c>
       <c r="R5" t="n">
-        <v>6781040</v>
+        <v>6781179</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1096,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 bild på garn i två tallar, rikligt på flera stammarna i omgivningen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,14 +1127,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130930038</v>
+        <v>130929896</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1148,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473380</v>
+        <v>473383</v>
       </c>
       <c r="R6" t="n">
-        <v>6781077</v>
+        <v>6781040</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,50 +1234,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130926931</v>
+        <v>130930038</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473279</v>
+        <v>473380</v>
       </c>
       <c r="R7" t="n">
-        <v>6781233</v>
+        <v>6781077</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130925631</v>
+        <v>130930105</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473220</v>
+        <v>473356</v>
       </c>
       <c r="R8" t="n">
-        <v>6781240</v>
+        <v>6781127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>1 bild på bandad tall. Rikligt på flera tallar i omgivningen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,14 +1453,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130929660</v>
+        <v>130930173</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1484,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473401</v>
+        <v>473286</v>
       </c>
       <c r="R9" t="n">
-        <v>6781091</v>
+        <v>6781163</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1538,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 bilder på tallar</t>
+          <t>Rikligt på några tallar i omgivningen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,14 +1565,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130926030</v>
+        <v>130930241</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473268</v>
+        <v>473245</v>
       </c>
       <c r="R10" t="n">
-        <v>6781239</v>
+        <v>6781194</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,7 +1650,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3 bilder, 1 som miljöbild på torrakor</t>
+          <t>Rikligt på flera tallar i omgivningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130927174</v>
+        <v>130925631</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1684,37 +1688,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473354</v>
+        <v>473220</v>
       </c>
       <c r="R11" t="n">
-        <v>6781177</v>
+        <v>6781240</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,7 +1767,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på några stammar i omgivningen. 3 Miljöbilder för området</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,7 +1776,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1789,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130930105</v>
+        <v>130930035</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,34 +1805,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473356</v>
+        <v>473380</v>
       </c>
       <c r="R12" t="n">
-        <v>6781127</v>
+        <v>6781077</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,7 +1887,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 bild på bandad tall. Rikligt på flera tallar i omgivningen</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,35 +1914,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130926976</v>
+        <v>130926931</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
@@ -1982,11 +2000,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 bild på tall. Rikligt på flera tallar i omgivningen</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,53 +2026,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130930035</v>
+        <v>130929660</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rädbjörka, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473380</v>
+        <v>473401</v>
       </c>
       <c r="R14" t="n">
-        <v>6781077</v>
+        <v>6781091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2111,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på tallar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,14 +2138,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130928099</v>
+        <v>130929811</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473380</v>
+        <v>473446</v>
       </c>
       <c r="R15" t="n">
-        <v>6781179</v>
+        <v>6781033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,11 +2219,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bild på garn i två tallar, rikligt på flera stammarna i omgivningen</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 62620-2025 artfynd.xlsx
+++ b/artfynd/A 62620-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130926030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130926976</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130927174</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130928099</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130929660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130929811</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130929896</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930038</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930105</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930173</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930241</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2010,6 +2070,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130925631</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2130,6 +2195,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130930035</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,8 +2312,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130926931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>